--- a/artfynd/A 41020-2022 artfynd.xlsx
+++ b/artfynd/A 41020-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41020-2022 artfynd.xlsx
+++ b/artfynd/A 41020-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9079,228 +9079,6 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>114461582</v>
-      </c>
-      <c r="B77" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Kärrbäck 2, Upl</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>603400</v>
-      </c>
-      <c r="R77" t="n">
-        <v>6668601</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>C-Heb-0218</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Karolin Ring</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>114461583</v>
-      </c>
-      <c r="B78" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Kärrbäck 2, Upl</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>603383</v>
-      </c>
-      <c r="R78" t="n">
-        <v>6668493</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>C-Heb-0217</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Karolin Ring</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
